--- a/ZonasEscolares/excels/CALLAO-CALLAO-VENTANILLA.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-VENTANILLA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CALLAO-CALLAO-VENTANILLA.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-VENTANILLA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>123 VIRGEN DE LA ASUNCION</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.83615</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.15890400000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>290</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.83615</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.158904</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>60</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.872779</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.122767</v>
-      </c>
-      <c r="I3" t="n">
-        <v>217</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.872779</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.122767</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>74 LOS PROCERES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.866048</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.11444899999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>296</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.866048</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.114449</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>83 AMIGOS DE JESUS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.829997</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.12016300000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>304</v>
-      </c>
-      <c r="J5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.829997</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.120163</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>93 VIRGEN MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.875157</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.10725499999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>339</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.875157</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.107255</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>102 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.943642</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.11399900000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>246</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.943642</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.113999</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>104 MI PEQUEÑO GRAN MUNDO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.890433</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.12714099999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>264</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.890433</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.127141</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>106</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.87738</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.11657</v>
-      </c>
-      <c r="I9" t="n">
-        <v>228</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.87738</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.11657</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>107 LOS PASTORCITOS DE FATIMA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.886057</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.132603</v>
-      </c>
-      <c r="I10" t="n">
-        <v>290</v>
-      </c>
-      <c r="J10" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.886057</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.132603</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>114 CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.824778</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.13123299999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>296</v>
-      </c>
-      <c r="J11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.824778</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.131233</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>132 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.898898</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.128252</v>
-      </c>
-      <c r="I12" t="n">
-        <v>291</v>
-      </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.898898</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.128252</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>DIVINO NIÑO DE VILLA LOS REYES</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.8282</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.122204</v>
-      </c>
-      <c r="I13" t="n">
-        <v>204</v>
-      </c>
-      <c r="J13" t="n">
-        <v>11</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.8282</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.122204</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>4020 JOSE SANTOS CHOCANO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.8709</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.1148</v>
-      </c>
-      <c r="I14" t="n">
-        <v>770</v>
-      </c>
-      <c r="J14" t="n">
-        <v>33</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.8709</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.1148</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>4021</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.94362</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.114256</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J15" t="n">
-        <v>52</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.94362</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.114256</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>5051 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.871104</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.114307</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1791</v>
-      </c>
-      <c r="J16" t="n">
-        <v>68</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.871104</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.114307</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1791</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>5052 VIRGEN DE LA MERCED</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.875876</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.124247</v>
-      </c>
-      <c r="I17" t="n">
-        <v>931</v>
-      </c>
-      <c r="J17" t="n">
-        <v>37</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.875876</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.124247</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>5053 VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.876105</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.125546</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1287</v>
-      </c>
-      <c r="J18" t="n">
-        <v>53</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.876105</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.125546</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>5077 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.8308</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.1225</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1304</v>
-      </c>
-      <c r="J19" t="n">
-        <v>56</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.8308</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.1225</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>5086 POLITECNICO DE VENTANILLA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.882365</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.130585</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1847</v>
-      </c>
-      <c r="J20" t="n">
-        <v>85</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.882365</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.130585</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1847</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>5087</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.823805</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.127486</v>
-      </c>
-      <c r="I21" t="n">
-        <v>404</v>
-      </c>
-      <c r="J21" t="n">
-        <v>18</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.823805</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.127486</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>5088 HEROES DEL PACIFICO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.889443</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.13008600000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1364</v>
-      </c>
-      <c r="J22" t="n">
-        <v>50</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.889443</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.130086</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>5090 ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.89357</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.109993</v>
-      </c>
-      <c r="I23" t="n">
-        <v>787</v>
-      </c>
-      <c r="J23" t="n">
-        <v>34</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.89357</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.109993</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>5091 HIJOS DE GRAU</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.886214</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.132396</v>
-      </c>
-      <c r="I24" t="n">
-        <v>483</v>
-      </c>
-      <c r="J24" t="n">
-        <v>19</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.886214</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.132396</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>5093 ANTONIO RAYMONDI</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.885733</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.12378</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1489</v>
-      </c>
-      <c r="J25" t="n">
-        <v>57</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.885733</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.12378</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1489</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>5094 NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.827088</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.129217</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1094</v>
-      </c>
-      <c r="J26" t="n">
-        <v>46</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.827088</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.129217</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>5096</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-11.877161</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.116951</v>
-      </c>
-      <c r="I27" t="n">
-        <v>659</v>
-      </c>
-      <c r="J27" t="n">
-        <v>22</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-11.877161</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.116951</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>5116 DIVINO CREADOR</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-11.845586</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.12594799999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>394</v>
-      </c>
-      <c r="J28" t="n">
-        <v>18</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-11.845586</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.125948</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>LICEO NAVAL CAPITAN DE CORBETA MANUEL CLAVERO MUGA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-11.888391</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.128991</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1018</v>
-      </c>
-      <c r="J29" t="n">
-        <v>79</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-11.888391</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.128991</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>NUESTRA SEÑORA DE BELEN</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-11.873055</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.119737</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1243</v>
-      </c>
-      <c r="J30" t="n">
-        <v>53</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-11.873055</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.119737</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>POLITECNICO VILLA LOS REYES</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-11.8291</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.1267</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1218</v>
-      </c>
-      <c r="J31" t="n">
-        <v>66</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-11.8291</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.1267</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>5117 JORGE PORTOCARRERO REBAZA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-11.844911</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.147329</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1848</v>
-      </c>
-      <c r="J32" t="n">
-        <v>73</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-11.844911</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.147329</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>5118 COMANDANTE JUAN VALER SANDOVAL</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-11.876555</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.138679</v>
-      </c>
-      <c r="I33" t="n">
-        <v>844</v>
-      </c>
-      <c r="J33" t="n">
-        <v>28</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-11.876555</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.138679</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>5120 JOSE CARLOS MARIATEGUI LA CHIRA</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-11.83304</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.1254</v>
-      </c>
-      <c r="I34" t="n">
-        <v>458</v>
-      </c>
-      <c r="J34" t="n">
-        <v>19</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-11.83304</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.1254</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>5121 PEDRO PLANAS SILVA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-11.825204</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.1362</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1184</v>
-      </c>
-      <c r="J35" t="n">
-        <v>53</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-11.825204</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.1362</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1184</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>5122 JOSE ANDRES RAZURI ESTEVEZ</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-11.84698</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.130321</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1450</v>
-      </c>
-      <c r="J36" t="n">
-        <v>55</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-11.84698</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.130321</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>5123 FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-11.821738</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.138676</v>
-      </c>
-      <c r="I37" t="n">
-        <v>981</v>
-      </c>
-      <c r="J37" t="n">
-        <v>36</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-11.821738</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.138676</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>5125</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-11.831639</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.139366</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1895</v>
-      </c>
-      <c r="J38" t="n">
-        <v>65</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-11.831639</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.139366</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1895</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>5124 LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-11.833957</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.140243</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1571</v>
-      </c>
-      <c r="J39" t="n">
-        <v>58</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-11.833957</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.140243</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-11.882492</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.12990600000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>366</v>
-      </c>
-      <c r="J40" t="n">
-        <v>20</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-11.882492</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.129906</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-11.887057</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.11967</v>
-      </c>
-      <c r="I41" t="n">
-        <v>445</v>
-      </c>
-      <c r="J41" t="n">
-        <v>32</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-11.887057</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.11967</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>SAN PEDRO NOLASCO</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-11.878471</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-77.13382799999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>275</v>
-      </c>
-      <c r="J42" t="n">
-        <v>19</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-11.878471</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-77.133828</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>FE Y ALEGRIA 43</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-11.8223</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.13079999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1263</v>
-      </c>
-      <c r="J43" t="n">
-        <v>64</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-11.8223</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.1308</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>COLEGIO DE JESUS</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-11.887405</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-77.129215</v>
-      </c>
-      <c r="I44" t="n">
-        <v>201</v>
-      </c>
-      <c r="J44" t="n">
-        <v>12</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-11.887405</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-77.129215</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>SOPHIANO COLLEGE S.R.L.</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-11.8721</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-77.1281</v>
-      </c>
-      <c r="I45" t="n">
-        <v>428</v>
-      </c>
-      <c r="J45" t="n">
-        <v>22</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-11.8721</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-77.1281</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>SAN JUDAS TADEO PATRON DE LOS NIÑOS</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-11.8777</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-77.13500000000001</v>
-      </c>
-      <c r="I46" t="n">
-        <v>343</v>
-      </c>
-      <c r="J46" t="n">
-        <v>12</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-11.8777</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-77.135</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>AVHALDIM</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-11.869103</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.115948</v>
-      </c>
-      <c r="I47" t="n">
-        <v>375</v>
-      </c>
-      <c r="J47" t="n">
-        <v>37</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-11.869103</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.115948</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>FE Y ALEGRIA 29</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-11.8748</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-77.1071</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1129</v>
-      </c>
-      <c r="J48" t="n">
-        <v>55</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-11.8748</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-77.1071</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>CONSORCIO EDUCATIVO FK</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-11.875674</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-77.123238</v>
-      </c>
-      <c r="I49" t="n">
-        <v>282</v>
-      </c>
-      <c r="J49" t="n">
-        <v>18</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-11.875674</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-77.123238</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>HARRY SULLIVAN</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-11.937548</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-77.13420000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>222</v>
-      </c>
-      <c r="J50" t="n">
-        <v>11</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-11.937548</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-77.1342</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>ARTURO PADILLA ESPINOZA</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-11.86003</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-77.124549</v>
-      </c>
-      <c r="I51" t="n">
-        <v>307</v>
-      </c>
-      <c r="J51" t="n">
-        <v>16</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-11.86003</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-77.124549</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-11.82674</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-77.12656</v>
-      </c>
-      <c r="I52" t="n">
-        <v>532</v>
-      </c>
-      <c r="J52" t="n">
-        <v>31</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-11.82674</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-77.12656</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>3720 NUESTRA SEÑORA DE LA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-11.825532</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-77.12359600000001</v>
-      </c>
-      <c r="I53" t="n">
-        <v>921</v>
-      </c>
-      <c r="J53" t="n">
-        <v>44</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-11.825532</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-77.123596</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>5146</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-11.8563</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-77.1454</v>
-      </c>
-      <c r="I54" t="n">
-        <v>475</v>
-      </c>
-      <c r="J54" t="n">
-        <v>20</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-11.8563</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-77.1454</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>5127 MARTIR JOSE OLAYA</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-11.838755</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-77.123463</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1940</v>
-      </c>
-      <c r="J55" t="n">
-        <v>80</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-11.838755</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-77.123463</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>5144 DIVINO CRISTO EN LAS ALTURAS</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-11.829154</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-77.171516</v>
-      </c>
-      <c r="I56" t="n">
-        <v>466</v>
-      </c>
-      <c r="J56" t="n">
-        <v>20</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-11.829154</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-77.171516</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>ESCUELA HOGAR</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-11.841995</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-77.13551</v>
-      </c>
-      <c r="I57" t="n">
-        <v>324</v>
-      </c>
-      <c r="J57" t="n">
-        <v>26</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-11.841995</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-77.13551</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>5142 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-11.8425</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-77.1395</v>
-      </c>
-      <c r="I58" t="n">
-        <v>898</v>
-      </c>
-      <c r="J58" t="n">
-        <v>39</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-11.8425</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-77.1395</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>TRENTO</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-11.888839</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-77.116488</v>
-      </c>
-      <c r="I59" t="n">
-        <v>242</v>
-      </c>
-      <c r="J59" t="n">
-        <v>24</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-11.888839</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-77.116488</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>EVARISTE GALOIS</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-11.83892</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-77.14585</v>
-      </c>
-      <c r="I60" t="n">
-        <v>258</v>
-      </c>
-      <c r="J60" t="n">
-        <v>19</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-11.83892</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-77.14585</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>CORAZON DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-11.853539</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-77.142888</v>
-      </c>
-      <c r="I61" t="n">
-        <v>269</v>
-      </c>
-      <c r="J61" t="n">
-        <v>17</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-11.853539</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-77.142888</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>CESAR VALLEJO DE VENTANILLA</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-11.819436</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-77.138379</v>
-      </c>
-      <c r="I62" t="n">
-        <v>248</v>
-      </c>
-      <c r="J62" t="n">
-        <v>22</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-11.819436</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-77.138379</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>LA SAGRADA FAMILIA</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-11.834481</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-77.16302399999999</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-11.834481</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-77.163024</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>ESCUELA HOGAR COMUNITARIA REGIONAL SAGRADA FAMILIA</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-11.827007</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-77.131846</v>
-      </c>
-      <c r="I64" t="n">
-        <v>911</v>
-      </c>
-      <c r="J64" t="n">
-        <v>46</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-11.827007</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-77.131846</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>LUISA ASTRAIN</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-11.835376</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-77.17481600000001</v>
-      </c>
-      <c r="I65" t="n">
-        <v>398</v>
-      </c>
-      <c r="J65" t="n">
-        <v>27</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-11.835376</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-77.174816</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-11.826084</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-77.13137399999999</v>
-      </c>
-      <c r="I66" t="n">
-        <v>277</v>
-      </c>
-      <c r="J66" t="n">
-        <v>19</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-11.826084</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-77.131374</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>120 LAS CASUARINAS</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-11.831193</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-77.14366</v>
-      </c>
-      <c r="I67" t="n">
-        <v>238</v>
-      </c>
-      <c r="J67" t="n">
-        <v>10</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-11.831193</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-77.14366</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>JESUCRISTO MI PASTOR</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-11.844779</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-77.155433</v>
-      </c>
-      <c r="I68" t="n">
-        <v>212</v>
-      </c>
-      <c r="J68" t="n">
-        <v>18</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-11.844779</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-77.155433</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>5129 VENCEDORES DE PACHACUTEC</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-11.831957</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-77.14787200000001</v>
-      </c>
-      <c r="I69" t="n">
-        <v>754</v>
-      </c>
-      <c r="J69" t="n">
-        <v>31</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-11.831957</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-77.147872</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>COPRODELI SAN MARTIN</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-11.831507</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-77.15848800000001</v>
-      </c>
-      <c r="I70" t="n">
-        <v>448</v>
-      </c>
-      <c r="J70" t="n">
-        <v>24</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-11.831507</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-77.158488</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>5128 SAGRADO CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-11.835</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-77.1597</v>
-      </c>
-      <c r="I71" t="n">
-        <v>1746</v>
-      </c>
-      <c r="J71" t="n">
-        <v>69</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-11.835</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-77.1597</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1746</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>COPRODELI SAN JUAN MACIAS</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-11.829559</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-77.1472</v>
-      </c>
-      <c r="I72" t="n">
-        <v>626</v>
-      </c>
-      <c r="J72" t="n">
-        <v>23</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-11.829559</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-77.1472</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>122 CARITAS FELICES</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-11.832601</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-77.14759100000001</v>
-      </c>
-      <c r="I73" t="n">
-        <v>285</v>
-      </c>
-      <c r="J73" t="n">
-        <v>14</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-11.832601</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-77.147591</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>5130 PACHACUTEC</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-11.829203</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-77.15527400000001</v>
-      </c>
-      <c r="I74" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J74" t="n">
-        <v>75</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-11.829203</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-77.155274</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>5130-1 LOS LICENCIADOS</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-11.8787</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-77.13167</v>
-      </c>
-      <c r="I75" t="n">
-        <v>528</v>
-      </c>
-      <c r="J75" t="n">
-        <v>20</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-11.8787</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-77.13167</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>COPRODELI SAN FRANCISCO SOLANO</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-11.835969</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-77.16091900000001</v>
-      </c>
-      <c r="I76" t="n">
-        <v>708</v>
-      </c>
-      <c r="J76" t="n">
-        <v>32</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-11.835969</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-77.160919</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>SANTA MARIA DE PACHACUTEC</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-11.830843</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-77.160814</v>
-      </c>
-      <c r="I77" t="n">
-        <v>325</v>
-      </c>
-      <c r="J77" t="n">
-        <v>19</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-11.830843</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-77.160814</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>HEROES DEL PACIFICO</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-11.872384</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-77.142034</v>
-      </c>
-      <c r="I78" t="n">
-        <v>289</v>
-      </c>
-      <c r="J78" t="n">
-        <v>25</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-11.872384</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-77.142034</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>5130-3 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-11.938141</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-77.136459</v>
-      </c>
-      <c r="I79" t="n">
-        <v>573</v>
-      </c>
-      <c r="J79" t="n">
-        <v>30</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-11.938141</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-77.136459</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>5145</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-11.853298</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-77.138857</v>
-      </c>
-      <c r="I80" t="n">
-        <v>498</v>
-      </c>
-      <c r="J80" t="n">
-        <v>18</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-11.853298</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-77.138857</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>INMACULADA CONCEPCION DE LA SANTISIMA VIRGEN DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-11.8319</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-77.1592</v>
-      </c>
-      <c r="I81" t="n">
-        <v>258</v>
-      </c>
-      <c r="J81" t="n">
-        <v>15</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-11.8319</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-77.1592</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>125 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-11.8433</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-77.1283</v>
-      </c>
-      <c r="I82" t="n">
-        <v>280</v>
-      </c>
-      <c r="J82" t="n">
-        <v>10</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-11.8433</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-77.1283</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>FE Y ALEGRIA 59</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-11.84209</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-77.13436</v>
-      </c>
-      <c r="I83" t="n">
-        <v>993</v>
-      </c>
-      <c r="J83" t="n">
-        <v>53</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-11.84209</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-77.13436</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>5138 DEFENSORES DE LA PATRIA</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-11.8798</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-77.1378</v>
-      </c>
-      <c r="I84" t="n">
-        <v>524</v>
-      </c>
-      <c r="J84" t="n">
-        <v>32</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-11.8798</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-77.1378</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>126</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-11.878733</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-77.128305</v>
-      </c>
-      <c r="I85" t="n">
-        <v>350</v>
-      </c>
-      <c r="J85" t="n">
-        <v>13</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-11.878733</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-77.128305</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>5137</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-11.8776</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-77.1052</v>
-      </c>
-      <c r="I86" t="n">
-        <v>687</v>
-      </c>
-      <c r="J86" t="n">
-        <v>33</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-11.8776</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-77.1052</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>ALFA</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-11.871729</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-77.117287</v>
-      </c>
-      <c r="I87" t="n">
-        <v>286</v>
-      </c>
-      <c r="J87" t="n">
-        <v>25</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-11.871729</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-77.117287</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>127</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-11.879607</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-77.137528</v>
-      </c>
-      <c r="I88" t="n">
-        <v>338</v>
-      </c>
-      <c r="J88" t="n">
-        <v>13</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-11.879607</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-77.137528</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>UNION Y PORVENIR</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-11.840062</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-77.122462</v>
-      </c>
-      <c r="I89" t="n">
-        <v>260</v>
-      </c>
-      <c r="J89" t="n">
-        <v>16</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-11.840062</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-77.122462</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>GUIA DIVINA</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-11.894318</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-77.128783</v>
-      </c>
-      <c r="I90" t="n">
-        <v>263</v>
-      </c>
-      <c r="J90" t="n">
-        <v>23</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-11.894318</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-77.128783</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>5141 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-11.837874</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-77.124257</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1141</v>
-      </c>
-      <c r="J91" t="n">
-        <v>45</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-11.837874</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-77.124257</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>NUESTRA SEÑORA DE BELEN</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-11.873055</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-77.119737</v>
-      </c>
-      <c r="I92" t="n">
-        <v>620</v>
-      </c>
-      <c r="J92" t="n">
-        <v>20</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-11.873055</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-77.119737</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>5140 PRESIDENTE DE LA REPUBLICA DE COLOMBIA - DR ALVARO URIBE VELEZ</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-11.845486</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-77.137455</v>
-      </c>
-      <c r="I93" t="n">
-        <v>551</v>
-      </c>
-      <c r="J93" t="n">
-        <v>23</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-11.845486</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-77.137455</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>COPRODELI SANTA MARIA ASUNTA AL CIELO</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-11.849816</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-77.145747</v>
-      </c>
-      <c r="I94" t="n">
-        <v>716</v>
-      </c>
-      <c r="J94" t="n">
-        <v>33</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-11.849816</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-77.145747</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>143 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-11.880825</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-77.099523</v>
-      </c>
-      <c r="I95" t="n">
-        <v>209</v>
-      </c>
-      <c r="J95" t="n">
-        <v>11</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-11.880825</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-77.099523</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>PRINCIPE DE ASTURIAS</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-11.874609</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-77.116416</v>
-      </c>
-      <c r="I96" t="n">
-        <v>267</v>
-      </c>
-      <c r="J96" t="n">
-        <v>20</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-11.874609</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-77.116416</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>145</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-11.8546</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-77.14004300000001</v>
-      </c>
-      <c r="I97" t="n">
-        <v>215</v>
-      </c>
-      <c r="J97" t="n">
-        <v>9</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-11.8546</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-77.140043</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>FE Y ALEGRIA 76</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-11.84773</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-77.145983</v>
-      </c>
-      <c r="I98" t="n">
-        <v>885</v>
-      </c>
-      <c r="J98" t="n">
-        <v>36</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-11.84773</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-77.145983</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>157</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-11.8464</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-77.1352</v>
-      </c>
-      <c r="I99" t="n">
-        <v>122</v>
-      </c>
-      <c r="J99" t="n">
-        <v>5</v>
-      </c>
-      <c r="K99" t="n">
-        <v>1</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-11.8464</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-77.1352</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>155 SAN MIGUEL ARCANGEL</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-11.827305</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-77.156629</v>
-      </c>
-      <c r="I100" t="n">
-        <v>270</v>
-      </c>
-      <c r="J100" t="n">
-        <v>10</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-11.827305</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-77.156629</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>5147</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-11.843993</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-77.128533</v>
-      </c>
-      <c r="I101" t="n">
-        <v>372</v>
-      </c>
-      <c r="J101" t="n">
-        <v>12</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-11.843993</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-77.128533</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>ANGELES DE SAN PEDRO</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-11.830086</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-77.160438</v>
-      </c>
-      <c r="I102" t="n">
-        <v>269</v>
-      </c>
-      <c r="J102" t="n">
-        <v>15</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-11.830086</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-77.160438</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>5149</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-11.848</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-77.1401</v>
-      </c>
-      <c r="I103" t="n">
-        <v>706</v>
-      </c>
-      <c r="J103" t="n">
-        <v>27</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-11.848</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-77.1401</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>5148 LAS BRISAS DE PACHACUTEC</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-11.84639</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-77.12362400000001</v>
-      </c>
-      <c r="I104" t="n">
-        <v>333</v>
-      </c>
-      <c r="J104" t="n">
-        <v>15</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-11.84639</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-77.123624</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5877,20 +6895,30 @@
           <t>5150</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>-11.8512</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-77.15009999999999</v>
-      </c>
-      <c r="I105" t="n">
-        <v>473</v>
-      </c>
-      <c r="J105" t="n">
-        <v>22</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-11.8512</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-77.1501</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5929,20 +6957,30 @@
           <t>CONSORCIO EDUCATIVO FK</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>-11.875674</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-77.123238</v>
-      </c>
-      <c r="I106" t="n">
-        <v>322</v>
-      </c>
-      <c r="J106" t="n">
-        <v>16</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-11.875674</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-77.123238</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5981,20 +7019,30 @@
           <t>MIRAMAR</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>-11.835868</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-77.141908</v>
-      </c>
-      <c r="I107" t="n">
-        <v>200</v>
-      </c>
-      <c r="J107" t="n">
-        <v>13</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-11.835868</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-77.141908</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6033,20 +7081,30 @@
           <t>SAN JUAN DE DIOS TODOPODEROSO</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>-11.84131</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-77.12353899999999</v>
-      </c>
-      <c r="I108" t="n">
-        <v>252</v>
-      </c>
-      <c r="J108" t="n">
-        <v>14</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-11.84131</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-77.123539</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6085,20 +7143,30 @@
           <t>LATINO AMERICANO</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>-11.845557</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-77.154781</v>
-      </c>
-      <c r="I109" t="n">
-        <v>212</v>
-      </c>
-      <c r="J109" t="n">
-        <v>14</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-11.845557</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-77.154781</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6137,20 +7205,30 @@
           <t>5152</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>-11.838</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-77.169338</v>
-      </c>
-      <c r="I110" t="n">
-        <v>386</v>
-      </c>
-      <c r="J110" t="n">
-        <v>14</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-11.838</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-77.169338</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6189,20 +7267,30 @@
           <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
-      <c r="G111" t="n">
-        <v>-11.82866</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-77.157281</v>
-      </c>
-      <c r="I111" t="n">
-        <v>12</v>
-      </c>
-      <c r="J111" t="n">
-        <v>3</v>
-      </c>
-      <c r="K111" t="n">
-        <v>1</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-11.82866</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-77.157281</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6241,20 +7329,30 @@
           <t>5154 SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>-11.82743</v>
-      </c>
-      <c r="H112" t="n">
-        <v>-77.16229</v>
-      </c>
-      <c r="I112" t="n">
-        <v>231</v>
-      </c>
-      <c r="J112" t="n">
-        <v>14</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-11.82743</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-77.16229</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6293,20 +7391,30 @@
           <t>SANTA ELENA</t>
         </is>
       </c>
-      <c r="G113" t="n">
-        <v>-11.824442</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-77.126588</v>
-      </c>
-      <c r="I113" t="n">
-        <v>451</v>
-      </c>
-      <c r="J113" t="n">
-        <v>16</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-11.824442</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-77.126588</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6345,20 +7453,30 @@
           <t>GOZO ETERNO INCAWASI</t>
         </is>
       </c>
-      <c r="G114" t="n">
-        <v>-11.84386</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-77.157607</v>
-      </c>
-      <c r="I114" t="n">
-        <v>285</v>
-      </c>
-      <c r="J114" t="n">
-        <v>23</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-11.84386</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-77.157607</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6397,20 +7515,30 @@
           <t>ISAAC NEWTON E.I.R.L.</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>-11.887075</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-77.120113</v>
-      </c>
-      <c r="I115" t="n">
-        <v>838</v>
-      </c>
-      <c r="J115" t="n">
-        <v>38</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-11.887075</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-77.120113</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6449,20 +7577,30 @@
           <t>5156 ELIAS AGUIRRE ROMERO</t>
         </is>
       </c>
-      <c r="G116" t="n">
-        <v>-11.839988</v>
-      </c>
-      <c r="H116" t="n">
-        <v>-77.175173</v>
-      </c>
-      <c r="I116" t="n">
-        <v>689</v>
-      </c>
-      <c r="J116" t="n">
-        <v>27</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-11.839988</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-77.175173</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/CALLAO-CALLAO-VENTANILLA.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-VENTANILLA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>141868</t>
+          <t>587637</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>123 VIRGEN DE LA ASUNCION</t>
+          <t>120 LAS CASUARINAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.83615</t>
+          <t>-11.831193</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.158904</t>
+          <t>-77.14366</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>144305</t>
+          <t>594402</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>125 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.872779</t>
+          <t>-11.8433</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.122767</t>
+          <t>-77.1283</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>144329</t>
+          <t>678915</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74 LOS PROCERES</t>
+          <t>155 SAN MIGUEL ARCANGEL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.866048</t>
+          <t>-11.827305</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.114449</t>
+          <t>-77.156629</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>144334</t>
+          <t>144367</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>83 AMIGOS DE JESUS</t>
+          <t>102 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.829997</t>
+          <t>-11.943642</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.120163</t>
+          <t>-77.113999</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>144348</t>
+          <t>144372</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>93 VIRGEN MARIA AUXILIADORA</t>
+          <t>104 MI PEQUEÑO GRAN MUNDO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.875157</t>
+          <t>-11.890433</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.107255</t>
+          <t>-77.127141</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,27 +811,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>144367</t>
+          <t>144409</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>102 SEÑOR DE LOS MILAGROS</t>
+          <t>107 LOS PASTORCITOS DE FATIMA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.943642</t>
+          <t>-11.886057</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.113999</t>
+          <t>-77.132603</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>144372</t>
+          <t>144447</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>104 MI PEQUEÑO GRAN MUNDO</t>
+          <t>114 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.890433</t>
+          <t>-11.824778</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.127141</t>
+          <t>-77.131233</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>296</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>144391</t>
+          <t>144452</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>132 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.87738</t>
+          <t>-11.898898</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.11657</t>
+          <t>-77.128252</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,27 +997,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>144409</t>
+          <t>144503</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>107 LOS PASTORCITOS DE FATIMA</t>
+          <t>DIVINO NIÑO DE VILLA LOS REYES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.886057</t>
+          <t>-11.8282</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.132603</t>
+          <t>-77.122204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1059,27 +1059,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>144447</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>114 CORAZON DE JESUS</t>
+          <t>HARRY SULLIVAN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.824778</t>
+          <t>-11.937548</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.131233</t>
+          <t>-77.1342</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1121,27 +1121,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>144452</t>
+          <t>614240</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>132 SAGRADO CORAZON DE JESUS</t>
+          <t>143 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.898898</t>
+          <t>-11.880825</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.128252</t>
+          <t>-77.099523</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>144503</t>
+          <t>144329</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO DE VILLA LOS REYES</t>
+          <t>74 LOS PROCERES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.8282</t>
+          <t>-11.866048</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.122204</t>
+          <t>-77.114449</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>296</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>144517</t>
+          <t>145164</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4020 JOSE SANTOS CHOCANO</t>
+          <t>COLEGIO DE JESUS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.8709</t>
+          <t>-11.887405</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.1148</t>
+          <t>-77.129215</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>144522</t>
+          <t>145220</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>SAN JUDAS TADEO PATRON DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.94362</t>
+          <t>-11.8777</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.114256</t>
+          <t>-77.135</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>144536</t>
+          <t>684233</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5051 VIRGEN DE FATIMA</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.871104</t>
+          <t>-11.843993</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.114307</t>
+          <t>-77.128533</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>144541</t>
+          <t>144334</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5052 VIRGEN DE LA MERCED</t>
+          <t>83 AMIGOS DE JESUS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.875876</t>
+          <t>-11.829997</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.124247</t>
+          <t>-77.120163</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>144555</t>
+          <t>594529</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5053 VICTOR ANDRES BELAUNDE</t>
+          <t>126</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.876105</t>
+          <t>-11.878733</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.125546</t>
+          <t>-77.128305</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>144560</t>
+          <t>594553</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5077 JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>127</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.8308</t>
+          <t>-11.879607</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.1225</t>
+          <t>-77.137528</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>338</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>144579</t>
+          <t>805174</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5086 POLITECNICO DE VENTANILLA</t>
+          <t>MIRAMAR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.882365</t>
+          <t>-11.835868</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.130585</t>
+          <t>-77.141908</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>144584</t>
+          <t>144348</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>93 VIRGEN MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.823805</t>
+          <t>-11.875157</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.127486</t>
+          <t>-77.107255</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>339</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,42 +1741,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>144598</t>
+          <t>593676</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5088 HEROES DEL PACIFICO</t>
+          <t>122 CARITAS FELICES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.889443</t>
+          <t>-11.832601</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.130086</t>
+          <t>-77.147591</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>144602</t>
+          <t>820792</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5090 ANTONIA MORENO DE CACERES</t>
+          <t>SAN JUAN DE DIOS TODOPODEROSO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.89357</t>
+          <t>-11.84131</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.109993</t>
+          <t>-77.123539</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>144616</t>
+          <t>824912</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5091 HIJOS DE GRAU</t>
+          <t>LATINO AMERICANO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.886214</t>
+          <t>-11.845557</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.132396</t>
+          <t>-77.154781</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>144621</t>
+          <t>834548</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5093 ANTONIO RAYMONDI</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.885733</t>
+          <t>-11.838</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.12378</t>
+          <t>-77.169338</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>386</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>144635</t>
+          <t>844359</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>5094 NACIONES UNIDAS</t>
+          <t>5154 SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.827088</t>
+          <t>-11.82743</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.129217</t>
+          <t>-77.16229</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>144640</t>
+          <t>141868</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>123 VIRGEN DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.877161</t>
+          <t>-11.83615</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.116951</t>
+          <t>-77.158904</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>144664</t>
+          <t>594379</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>5116 DIVINO CREADOR</t>
+          <t>INMACULADA CONCEPCION DE LA SANTISIMA VIRGEN DEL ROSARIO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.845586</t>
+          <t>-11.8319</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.125948</t>
+          <t>-77.1592</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>144678</t>
+          <t>717281</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LICEO NAVAL CAPITAN DE CORBETA MANUEL CLAVERO MUGA</t>
+          <t>ANGELES DE SAN PEDRO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.888391</t>
+          <t>-11.830086</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.128991</t>
+          <t>-77.160438</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>269</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>144697</t>
+          <t>723324</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE BELEN</t>
+          <t>5148 LAS BRISAS DE PACHACUTEC</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.873055</t>
+          <t>-11.84639</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.119737</t>
+          <t>-77.123624</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>144701</t>
+          <t>145828</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>POLITECNICO VILLA LOS REYES</t>
+          <t>ARTURO PADILLA ESPINOZA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.8291</t>
+          <t>-11.86003</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.1267</t>
+          <t>-77.124549</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>144744</t>
+          <t>594690</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>5117 JORGE PORTOCARRERO REBAZA</t>
+          <t>UNION Y PORVENIR</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.844911</t>
+          <t>-11.840062</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.147329</t>
+          <t>-77.122462</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>144758</t>
+          <t>787207</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5118 COMANDANTE JUAN VALER SANDOVAL</t>
+          <t>CONSORCIO EDUCATIVO FK</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.876555</t>
+          <t>-11.875674</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.138679</t>
+          <t>-77.123238</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>322</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>144777</t>
+          <t>844528</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>5120 JOSE CARLOS MARIATEGUI LA CHIRA</t>
+          <t>SANTA ELENA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.83304</t>
+          <t>-11.824442</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.1254</t>
+          <t>-77.126588</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>451</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>144782</t>
+          <t>541885</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5121 PEDRO PLANAS SILVA</t>
+          <t>CORAZON DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.825204</t>
+          <t>-11.853539</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.1362</t>
+          <t>-77.142888</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>269</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>144796</t>
+          <t>144584</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5122 JOSE ANDRES RAZURI ESTEVEZ</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.84698</t>
+          <t>-11.823805</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.130321</t>
+          <t>-77.127486</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>404</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>144800</t>
+          <t>144664</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5123 FRANCISCO BOLOGNESI CERVANTES</t>
+          <t>5116 DIVINO CREADOR</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.821738</t>
+          <t>-11.845586</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.138676</t>
+          <t>-77.125948</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>394</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>145729</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>CONSORCIO EDUCATIVO FK</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.831639</t>
+          <t>-11.875674</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.139366</t>
+          <t>-77.123238</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>144824</t>
+          <t>588929</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5124 LIBERTADOR SIMON BOLIVAR</t>
+          <t>JESUCRISTO MI PASTOR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.833957</t>
+          <t>-11.844779</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.140243</t>
+          <t>-77.155433</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>144843</t>
+          <t>594157</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.882492</t>
+          <t>-11.853298</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.129906</t>
+          <t>-77.138857</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>498</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>144937</t>
+          <t>144616</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MARCELINO CHAMPAGNAT</t>
+          <t>5091 HIJOS DE GRAU</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.887057</t>
+          <t>-11.886214</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.11967</t>
+          <t>-77.132396</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>483</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>144942</t>
+          <t>144777</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAN PEDRO NOLASCO</t>
+          <t>5120 JOSE CARLOS MARIATEGUI LA CHIRA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.878471</t>
+          <t>-11.83304</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.133828</t>
+          <t>-77.1254</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>458</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>145140</t>
+          <t>144942</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 43</t>
+          <t>SAN PEDRO NOLASCO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.8223</t>
+          <t>-11.878471</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.1308</t>
+          <t>-77.133828</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>145164</t>
+          <t>527634</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>COLEGIO DE JESUS</t>
+          <t>EVARISTE GALOIS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.887405</t>
+          <t>-11.83892</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.129215</t>
+          <t>-77.14585</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>145178</t>
+          <t>582574</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SOPHIANO COLLEGE S.R.L.</t>
+          <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.8721</t>
+          <t>-11.826084</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.1281</t>
+          <t>-77.131374</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>145220</t>
+          <t>594044</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAN JUDAS TADEO PATRON DE LOS NIÑOS</t>
+          <t>SANTA MARIA DE PACHACUTEC</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.8777</t>
+          <t>-11.830843</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.135</t>
+          <t>-77.160814</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>145376</t>
+          <t>576441</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AVHALDIM</t>
+          <t>LA SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.869103</t>
+          <t>-11.834481</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.115948</t>
+          <t>-77.163024</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>145381</t>
+          <t>144843</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 29</t>
+          <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.8748</t>
+          <t>-11.882492</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.1071</t>
+          <t>-77.129906</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>366</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>145729</t>
+          <t>360356</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CONSORCIO EDUCATIVO FK</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.875674</t>
+          <t>-11.8563</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.123238</t>
+          <t>-77.1454</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>475</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>145734</t>
+          <t>509201</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HARRY SULLIVAN</t>
+          <t>5144 DIVINO CRISTO EN LAS ALTURAS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.937548</t>
+          <t>-11.829154</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.1342</t>
+          <t>-77.171516</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>466</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>145828</t>
+          <t>593959</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ARTURO PADILLA ESPINOZA</t>
+          <t>5130-1 LOS LICENCIADOS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.86003</t>
+          <t>-11.8787</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.124549</t>
+          <t>-77.13167</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>528</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>319885</t>
+          <t>595213</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>NUESTRA SEÑORA DE BELEN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.82674</t>
+          <t>-11.873055</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.12656</t>
+          <t>-77.119737</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>620</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>320105</t>
+          <t>618950</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>3720 NUESTRA SEÑORA DE LA MISERICORDIA</t>
+          <t>PRINCIPE DE ASTURIAS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.825532</t>
+          <t>-11.874609</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.123596</t>
+          <t>-77.116416</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>360356</t>
+          <t>144640</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.8563</t>
+          <t>-11.877161</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.1454</t>
+          <t>-77.116951</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>659</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>506472</t>
+          <t>145178</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>5127 MARTIR JOSE OLAYA</t>
+          <t>SOPHIANO COLLEGE S.R.L.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.838755</t>
+          <t>-11.8721</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.123463</t>
+          <t>-77.1281</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>428</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>509201</t>
+          <t>567880</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>5144 DIVINO CRISTO EN LAS ALTURAS</t>
+          <t>CESAR VALLEJO DE VENTANILLA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.829154</t>
+          <t>-11.819436</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.171516</t>
+          <t>-77.138379</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>509220</t>
+          <t>723338</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ESCUELA HOGAR</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-11.841995</t>
+          <t>-11.8512</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.13551</t>
+          <t>-77.1501</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>473</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>509239</t>
+          <t>593657</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>5142 VIRGEN DE GUADALUPE</t>
+          <t>COPRODELI SAN JUAN MACIAS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.8425</t>
+          <t>-11.829559</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.1395</t>
+          <t>-77.1472</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>626</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>524999</t>
+          <t>595086</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TRENTO</t>
+          <t>GUIA DIVINA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.888839</t>
+          <t>-11.894318</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.116488</t>
+          <t>-77.128783</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>527634</t>
+          <t>595411</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>EVARISTE GALOIS</t>
+          <t>5140 PRESIDENTE DE LA REPUBLICA DE COLOMBIA - DR ALVARO URIBE VELEZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.83892</t>
+          <t>-11.845486</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.14585</t>
+          <t>-77.137455</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>551</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>541885</t>
+          <t>845636</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CORAZON DE SANTA MARIA</t>
+          <t>GOZO ETERNO INCAWASI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.853539</t>
+          <t>-11.84386</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.142888</t>
+          <t>-77.157607</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>567880</t>
+          <t>524999</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO DE VENTANILLA</t>
+          <t>TRENTO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-11.819436</t>
+          <t>-11.888839</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.138379</t>
+          <t>-77.116488</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>576441</t>
+          <t>593624</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LA SAGRADA FAMILIA</t>
+          <t>COPRODELI SAN MARTIN</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.834481</t>
+          <t>-11.831507</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.163024</t>
+          <t>-77.158488</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>448</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>580283</t>
+          <t>594082</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ESCUELA HOGAR COMUNITARIA REGIONAL SAGRADA FAMILIA</t>
+          <t>HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.827007</t>
+          <t>-11.872384</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.131846</t>
+          <t>-77.142034</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>289</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>582338</t>
+          <t>594548</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LUISA ASTRAIN</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-11.835376</t>
+          <t>-11.871729</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.174816</t>
+          <t>-77.117287</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>286</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>582574</t>
+          <t>509220</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SAN LUIS GONZAGA</t>
+          <t>ESCUELA HOGAR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.826084</t>
+          <t>-11.841995</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.131374</t>
+          <t>-77.13551</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>587637</t>
+          <t>582338</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>120 LAS CASUARINAS</t>
+          <t>LUISA ASTRAIN</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.831193</t>
+          <t>-11.835376</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.14366</t>
+          <t>-77.174816</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>398</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>588929</t>
+          <t>722895</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>JESUCRISTO MI PASTOR</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-11.844779</t>
+          <t>-11.848</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.155433</t>
+          <t>-77.1401</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>706</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>593539</t>
+          <t>901712</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>5129 VENCEDORES DE PACHACUTEC</t>
+          <t>5156 ELIAS AGUIRRE ROMERO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-11.831957</t>
+          <t>-11.839988</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-77.147872</t>
+          <t>-77.175173</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>689</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>593624</t>
+          <t>144758</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>COPRODELI SAN MARTIN</t>
+          <t>5118 COMANDANTE JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-11.831507</t>
+          <t>-11.876555</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.158488</t>
+          <t>-77.138679</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>844</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>593638</t>
+          <t>836750</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>5128 SAGRADO CORAZON DE MARIA</t>
+          <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-11.835</t>
+          <t>-11.82866</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.1597</t>
+          <t>-77.157281</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>593657</t>
+          <t>594124</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>COPRODELI SAN JUAN MACIAS</t>
+          <t>5130-3 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-11.829559</t>
+          <t>-11.938141</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.1472</t>
+          <t>-77.136459</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>573</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>593676</t>
+          <t>319885</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>122 CARITAS FELICES</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-11.832601</t>
+          <t>-11.82674</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.147591</t>
+          <t>-77.12656</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>532</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>593940</t>
+          <t>593539</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>5130 PACHACUTEC</t>
+          <t>5129 VENCEDORES DE PACHACUTEC</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.829203</t>
+          <t>-11.831957</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.155274</t>
+          <t>-77.147872</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>754</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>593959</t>
+          <t>144937</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>5130-1 LOS LICENCIADOS</t>
+          <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-11.8787</t>
+          <t>-11.887057</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.13167</t>
+          <t>-77.11967</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>445</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>594044</t>
+          <t>594459</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE PACHACUTEC</t>
+          <t>5138 DEFENSORES DE LA PATRIA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-11.830843</t>
+          <t>-11.8798</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.160814</t>
+          <t>-77.1378</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>524</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>594082</t>
+          <t>144517</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HEROES DEL PACIFICO</t>
+          <t>4020 JOSE SANTOS CHOCANO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-11.872384</t>
+          <t>-11.8709</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.142034</t>
+          <t>-77.1148</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>770</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>594124</t>
+          <t>594534</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>5130-3 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-11.938141</t>
+          <t>-11.8776</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.136459</t>
+          <t>-77.1052</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>687</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>594157</t>
+          <t>611717</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>COPRODELI SANTA MARIA ASUNTA AL CIELO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-11.853298</t>
+          <t>-11.849816</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.138857</t>
+          <t>-77.145747</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>716</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>594379</t>
+          <t>144602</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION DE LA SANTISIMA VIRGEN DEL ROSARIO</t>
+          <t>5090 ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-11.8319</t>
+          <t>-11.89357</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.1592</t>
+          <t>-77.109993</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>787</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>594402</t>
+          <t>144800</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>125 DIVINO NIÑO JESUS</t>
+          <t>5123 FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.8433</t>
+          <t>-11.821738</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.1283</t>
+          <t>-77.138676</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>981</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>594435</t>
+          <t>625583</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 59</t>
+          <t>FE Y ALEGRIA 76</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.84209</t>
+          <t>-11.84773</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.13436</t>
+          <t>-77.145983</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>885</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>594459</t>
+          <t>144541</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>5138 DEFENSORES DE LA PATRIA</t>
+          <t>5052 VIRGEN DE LA MERCED</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.8798</t>
+          <t>-11.875876</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.1378</t>
+          <t>-77.124247</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>931</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>594529</t>
+          <t>145376</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>AVHALDIM</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-11.878733</t>
+          <t>-11.869103</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.128305</t>
+          <t>-77.115948</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>594534</t>
+          <t>862664</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>ISAAC NEWTON E.I.R.L.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-11.8776</t>
+          <t>-11.887075</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.1052</t>
+          <t>-77.120113</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>838</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>594548</t>
+          <t>509239</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>5142 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.871729</t>
+          <t>-11.8425</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.117287</t>
+          <t>-77.1395</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>898</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>594553</t>
+          <t>320105</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>3720 NUESTRA SEÑORA DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.879607</t>
+          <t>-11.825532</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.137528</t>
+          <t>-77.123596</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>921</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>594690</t>
+          <t>595171</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UNION Y PORVENIR</t>
+          <t>5141 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.840062</t>
+          <t>-11.837874</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.122462</t>
+          <t>-77.124257</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>595086</t>
+          <t>144635</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>GUIA DIVINA</t>
+          <t>5094 NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-11.894318</t>
+          <t>-11.827088</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.128783</t>
+          <t>-77.129217</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>595171</t>
+          <t>580283</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>5141 DIVINO MAESTRO</t>
+          <t>ESCUELA HOGAR COMUNITARIA REGIONAL SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-11.837874</t>
+          <t>-11.827007</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.124257</t>
+          <t>-77.131846</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>911</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>595213</t>
+          <t>678883</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE BELEN</t>
+          <t>157</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-11.873055</t>
+          <t>-11.8464</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.119737</t>
+          <t>-77.1352</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>122</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,42 +6143,42 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>595411</t>
+          <t>144598</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>5140 PRESIDENTE DE LA REPUBLICA DE COLOMBIA - DR ALVARO URIBE VELEZ</t>
+          <t>5088 HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.845486</t>
+          <t>-11.889443</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.137455</t>
+          <t>-77.130086</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>611717</t>
+          <t>144522</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>COPRODELI SANTA MARIA ASUNTA AL CIELO</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-11.849816</t>
+          <t>-11.94362</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.145747</t>
+          <t>-77.114256</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>614240</t>
+          <t>144555</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>143 MARIA PARADO DE BELLIDO</t>
+          <t>5053 VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-11.880825</t>
+          <t>-11.876105</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.099523</t>
+          <t>-77.125546</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>618950</t>
+          <t>144697</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PRINCIPE DE ASTURIAS</t>
+          <t>NUESTRA SEÑORA DE BELEN</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-11.874609</t>
+          <t>-11.873055</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.116416</t>
+          <t>-77.119737</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>623211</t>
+          <t>144782</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>5121 PEDRO PLANAS SILVA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-11.8546</t>
+          <t>-11.825204</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.140043</t>
+          <t>-77.1362</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>625583</t>
+          <t>594435</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 76</t>
+          <t>FE Y ALEGRIA 59</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-11.84773</t>
+          <t>-11.84209</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.145983</t>
+          <t>-77.13436</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>993</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,37 +6515,37 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>678883</t>
+          <t>144796</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>5122 JOSE ANDRES RAZURI ESTEVEZ</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-11.8464</t>
+          <t>-11.84698</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.1352</t>
+          <t>-77.130321</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>678915</t>
+          <t>145381</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>155 SAN MIGUEL ARCANGEL</t>
+          <t>FE Y ALEGRIA 29</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-11.827305</t>
+          <t>-11.8748</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.156629</t>
+          <t>-77.1071</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>684233</t>
+          <t>144560</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5077 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-11.843993</t>
+          <t>-11.8308</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.128533</t>
+          <t>-77.1225</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>717281</t>
+          <t>144621</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ANGELES DE SAN PEDRO</t>
+          <t>5093 ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-11.830086</t>
+          <t>-11.885733</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.160438</t>
+          <t>-77.12378</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>722895</t>
+          <t>144824</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5124 LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-11.848</t>
+          <t>-11.833957</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-77.1401</t>
+          <t>-77.140243</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>723324</t>
+          <t>145140</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>5148 LAS BRISAS DE PACHACUTEC</t>
+          <t>FE Y ALEGRIA 43</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-11.84639</t>
+          <t>-11.8223</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.123624</t>
+          <t>-77.1308</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>723338</t>
+          <t>144819</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-11.8512</t>
+          <t>-11.831639</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-77.1501</t>
+          <t>-77.139366</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>787207</t>
+          <t>144701</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CONSORCIO EDUCATIVO FK</t>
+          <t>POLITECNICO VILLA LOS REYES</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-11.875674</t>
+          <t>-11.8291</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.123238</t>
+          <t>-77.1267</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>805174</t>
+          <t>144536</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MIRAMAR</t>
+          <t>5051 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-11.835868</t>
+          <t>-11.871104</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-77.141908</t>
+          <t>-77.114307</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>820792</t>
+          <t>593638</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SAN JUAN DE DIOS TODOPODEROSO</t>
+          <t>5128 SAGRADO CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-11.84131</t>
+          <t>-11.835</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-77.123539</t>
+          <t>-77.1597</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>824912</t>
+          <t>144744</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LATINO AMERICANO</t>
+          <t>5117 JORGE PORTOCARRERO REBAZA</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-11.845557</t>
+          <t>-11.844911</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-77.154781</t>
+          <t>-77.147329</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>834548</t>
+          <t>593940</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5130 PACHACUTEC</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-11.838</t>
+          <t>-11.829203</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-77.169338</t>
+          <t>-77.155274</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7259,42 +7259,42 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>836750</t>
+          <t>144678</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA MERCED</t>
+          <t>LICEO NAVAL CAPITAN DE CORBETA MANUEL CLAVERO MUGA</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-11.82866</t>
+          <t>-11.888391</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-77.157281</t>
+          <t>-77.128991</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>844359</t>
+          <t>506472</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>5154 SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>5127 MARTIR JOSE OLAYA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-11.82743</t>
+          <t>-11.838755</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-77.16229</t>
+          <t>-77.123463</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>844528</t>
+          <t>144579</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SANTA ELENA</t>
+          <t>5086 POLITECNICO DE VENTANILLA</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-11.824442</t>
+          <t>-11.882365</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-77.126588</t>
+          <t>-77.130585</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>845636</t>
+          <t>144305</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>GOZO ETERNO INCAWASI</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-11.84386</t>
+          <t>-11.872779</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-77.157607</t>
+          <t>-77.122767</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7507,37 +7507,37 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>862664</t>
+          <t>144391</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON E.I.R.L.</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-11.887075</t>
+          <t>-11.87738</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-77.120113</t>
+          <t>-77.11657</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>901712</t>
+          <t>623211</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>5156 ELIAS AGUIRRE ROMERO</t>
+          <t>145</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-11.839988</t>
+          <t>-11.8546</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-77.175173</t>
+          <t>-77.140043</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">

--- a/ZonasEscolares/excels/CALLAO-CALLAO-VENTANILLA.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-VENTANILLA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>587637</t>
+          <t>901712</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>120 LAS CASUARINAS</t>
+          <t>5156 ELIAS AGUIRRE ROMERO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.831193</t>
+          <t>689</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.14366</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-11.839988</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.175173</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>594402</t>
+          <t>862664</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>125 DIVINO NIÑO JESUS</t>
+          <t>ISAAC NEWTON E.I.R.L.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.8433</t>
+          <t>838</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.1283</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-11.887075</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.120113</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>678915</t>
+          <t>845636</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>155 SAN MIGUEL ARCANGEL</t>
+          <t>GOZO ETERNO INCAWASI</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.827305</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.156629</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-11.84386</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.157607</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>144367</t>
+          <t>844528</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102 SEÑOR DE LOS MILAGROS</t>
+          <t>SANTA ELENA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.943642</t>
+          <t>451</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.113999</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-11.824442</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.126588</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>144372</t>
+          <t>844359</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>104 MI PEQUEÑO GRAN MUNDO</t>
+          <t>5154 SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.890433</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.127141</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-11.82743</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.16229</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>144409</t>
+          <t>836750</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>107 LOS PASTORCITOS DE FATIMA</t>
+          <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.886057</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.132603</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-11.82866</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.157281</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>144447</t>
+          <t>834548</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>114 CORAZON DE JESUS</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.824778</t>
+          <t>386</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.131233</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>-11.838</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.169338</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>144452</t>
+          <t>824912</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>132 SAGRADO CORAZON DE JESUS</t>
+          <t>LATINO AMERICANO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.898898</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.128252</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-11.845557</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.154781</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>144503</t>
+          <t>820792</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO DE VILLA LOS REYES</t>
+          <t>SAN JUAN DE DIOS TODOPODEROSO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.8282</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.122204</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-11.84131</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.123539</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>145734</t>
+          <t>805174</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HARRY SULLIVAN</t>
+          <t>MIRAMAR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.937548</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.1342</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-11.835868</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.141908</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>614240</t>
+          <t>787207</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>143 MARIA PARADO DE BELLIDO</t>
+          <t>CONSORCIO EDUCATIVO FK</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.880825</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.099523</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-11.875674</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.123238</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>144329</t>
+          <t>723338</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>74 LOS PROCERES</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.866048</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.114449</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>-11.8512</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.1501</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>145164</t>
+          <t>723324</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COLEGIO DE JESUS</t>
+          <t>5148 LAS BRISAS DE PACHACUTEC</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.887405</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.129215</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-11.84639</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.123624</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>145220</t>
+          <t>722895</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAN JUDAS TADEO PATRON DE LOS NIÑOS</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.8777</t>
+          <t>706</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.135</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-11.848</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.1401</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>684233</t>
+          <t>717281</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>ANGELES DE SAN PEDRO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.843993</t>
+          <t>269</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.128533</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-11.830086</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.160438</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>144334</t>
+          <t>684233</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>83 AMIGOS DE JESUS</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.829997</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.120163</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-11.843993</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.128533</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>594529</t>
+          <t>678915</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>155 SAN MIGUEL ARCANGEL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.878733</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.128305</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>-11.827305</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.156629</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>594553</t>
+          <t>678883</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>157</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.879607</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.137528</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>-11.8464</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.1352</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>805174</t>
+          <t>625583</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MIRAMAR</t>
+          <t>FE Y ALEGRIA 76</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.835868</t>
+          <t>885</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.141908</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-11.84773</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.145983</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>144348</t>
+          <t>623211</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>93 VIRGEN MARIA AUXILIADORA</t>
+          <t>145</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.875157</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.107255</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>-11.8546</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.140043</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>593676</t>
+          <t>618950</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>122 CARITAS FELICES</t>
+          <t>PRINCIPE DE ASTURIAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.832601</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.147591</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-11.874609</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.116416</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>820792</t>
+          <t>614240</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN JUAN DE DIOS TODOPODEROSO</t>
+          <t>143 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.84131</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.123539</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-11.880825</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.099523</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>824912</t>
+          <t>611717</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LATINO AMERICANO</t>
+          <t>COPRODELI SANTA MARIA ASUNTA AL CIELO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.845557</t>
+          <t>716</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.154781</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-11.849816</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.145747</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>834548</t>
+          <t>595411</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5140 PRESIDENTE DE LA REPUBLICA DE COLOMBIA - DR ALVARO URIBE VELEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.838</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.169338</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>-11.845486</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.137455</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>844359</t>
+          <t>595213</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>5154 SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>NUESTRA SEÑORA DE BELEN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.82743</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.16229</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-11.873055</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.119737</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>141868</t>
+          <t>595171</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>123 VIRGEN DE LA ASUNCION</t>
+          <t>5141 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.83615</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.158904</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-11.837874</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.124257</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>594379</t>
+          <t>595086</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION DE LA SANTISIMA VIRGEN DEL ROSARIO</t>
+          <t>GUIA DIVINA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.8319</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.1592</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-11.894318</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.128783</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>717281</t>
+          <t>594690</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ANGELES DE SAN PEDRO</t>
+          <t>UNION Y PORVENIR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.830086</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.160438</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>-11.840062</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.122462</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>723324</t>
+          <t>594553</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5148 LAS BRISAS DE PACHACUTEC</t>
+          <t>127</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.84639</t>
+          <t>338</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.123624</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-11.879607</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.137528</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>145828</t>
+          <t>594548</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ARTURO PADILLA ESPINOZA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.86003</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.124549</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-11.871729</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.117287</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>594690</t>
+          <t>594534</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UNION Y PORVENIR</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.840062</t>
+          <t>687</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.122462</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-11.8776</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.1052</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>787207</t>
+          <t>594529</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CONSORCIO EDUCATIVO FK</t>
+          <t>126</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.875674</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.123238</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>-11.878733</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.128305</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>844528</t>
+          <t>594459</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SANTA ELENA</t>
+          <t>5138 DEFENSORES DE LA PATRIA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.824442</t>
+          <t>524</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.126588</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>-11.8798</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.1378</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>541885</t>
+          <t>594435</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CORAZON DE SANTA MARIA</t>
+          <t>FE Y ALEGRIA 59</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.853539</t>
+          <t>993</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.142888</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>-11.84209</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.13436</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>144584</t>
+          <t>594402</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>125 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.823805</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.127486</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>-11.8433</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.1283</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>144664</t>
+          <t>594379</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5116 DIVINO CREADOR</t>
+          <t>INMACULADA CONCEPCION DE LA SANTISIMA VIRGEN DEL ROSARIO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.845586</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.125948</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>-11.8319</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.1592</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>145729</t>
+          <t>594157</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CONSORCIO EDUCATIVO FK</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.875674</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.123238</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-11.853298</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.138857</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>588929</t>
+          <t>594124</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JESUCRISTO MI PASTOR</t>
+          <t>5130-3 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.844779</t>
+          <t>573</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.155433</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-11.938141</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.136459</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>594157</t>
+          <t>594082</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.853298</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.138857</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>-11.872384</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.142034</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>144616</t>
+          <t>594044</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>5091 HIJOS DE GRAU</t>
+          <t>SANTA MARIA DE PACHACUTEC</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.886214</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.132396</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>-11.830843</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.160814</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>144777</t>
+          <t>593983</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5120 JOSE CARLOS MARIATEGUI LA CHIRA</t>
+          <t>COPRODELI SAN FRANCISCO SOLANO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.83304</t>
+          <t>708</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.1254</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>-11.835969</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.160919</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>144942</t>
+          <t>593959</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SAN PEDRO NOLASCO</t>
+          <t>5130-1 LOS LICENCIADOS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.878471</t>
+          <t>528</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.133828</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-11.8787</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.13167</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>527634</t>
+          <t>593940</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EVARISTE GALOIS</t>
+          <t>5130 PACHACUTEC</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.83892</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.14585</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-11.829203</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.155274</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>582574</t>
+          <t>593676</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SAN LUIS GONZAGA</t>
+          <t>122 CARITAS FELICES</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.826084</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.131374</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-11.832601</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.147591</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>594044</t>
+          <t>593657</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE PACHACUTEC</t>
+          <t>COPRODELI SAN JUAN MACIAS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.830843</t>
+          <t>626</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.160814</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-11.829559</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.1472</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>576441</t>
+          <t>593638</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LA SAGRADA FAMILIA</t>
+          <t>5128 SAGRADO CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.834481</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.163024</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-11.835</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-77.1597</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>144843</t>
+          <t>593624</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU</t>
+          <t>COPRODELI SAN MARTIN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.882492</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.129906</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>-11.831507</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.158488</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>360356</t>
+          <t>593539</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5129 VENCEDORES DE PACHACUTEC</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.8563</t>
+          <t>754</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.1454</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>-11.831957</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.147872</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>509201</t>
+          <t>588929</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5144 DIVINO CRISTO EN LAS ALTURAS</t>
+          <t>JESUCRISTO MI PASTOR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.829154</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.171516</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>-11.844779</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.155433</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>593959</t>
+          <t>587637</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5130-1 LOS LICENCIADOS</t>
+          <t>120 LAS CASUARINAS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.8787</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.13167</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>-11.831193</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.14366</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>595213</t>
+          <t>582574</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE BELEN</t>
+          <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.873055</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.119737</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>-11.826084</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.131374</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>618950</t>
+          <t>582338</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PRINCIPE DE ASTURIAS</t>
+          <t>LUISA ASTRAIN</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.874609</t>
+          <t>398</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.116416</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-11.835376</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.174816</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>144640</t>
+          <t>580283</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>ESCUELA HOGAR COMUNITARIA REGIONAL SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.877161</t>
+          <t>911</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.116951</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>-11.827007</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.131846</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,37 +3787,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>145178</t>
+          <t>576441</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SOPHIANO COLLEGE S.R.L.</t>
+          <t>LA SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.8721</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.1281</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>-11.834481</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.163024</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3859,22 +3859,22 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>-11.819436</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>-77.138379</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>723338</t>
+          <t>541885</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>CORAZON DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-11.8512</t>
+          <t>269</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.1501</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>-11.853539</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.142888</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>593657</t>
+          <t>527634</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>COPRODELI SAN JUAN MACIAS</t>
+          <t>EVARISTE GALOIS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.829559</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.1472</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>-11.83892</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.14585</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>595086</t>
+          <t>524999</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GUIA DIVINA</t>
+          <t>TRENTO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.894318</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.128783</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-11.888839</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.116488</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>595411</t>
+          <t>509239</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>5140 PRESIDENTE DE LA REPUBLICA DE COLOMBIA - DR ALVARO URIBE VELEZ</t>
+          <t>5142 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.845486</t>
+          <t>898</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.137455</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>-11.8425</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.1395</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>845636</t>
+          <t>509220</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GOZO ETERNO INCAWASI</t>
+          <t>ESCUELA HOGAR</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.84386</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.157607</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-11.841995</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.13551</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>524999</t>
+          <t>509201</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TRENTO</t>
+          <t>5144 DIVINO CRISTO EN LAS ALTURAS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-11.888839</t>
+          <t>466</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.116488</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-11.829154</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.171516</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>593624</t>
+          <t>506472</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>COPRODELI SAN MARTIN</t>
+          <t>5127 MARTIR JOSE OLAYA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.831507</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.158488</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>-11.838755</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.123463</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>594082</t>
+          <t>360356</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HEROES DEL PACIFICO</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.872384</t>
+          <t>475</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.142034</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>-11.8563</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.1454</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>594548</t>
+          <t>320105</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>3720 NUESTRA SEÑORA DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-11.871729</t>
+          <t>921</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.117287</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>-11.825532</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.123596</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>509220</t>
+          <t>319885</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ESCUELA HOGAR</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.841995</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.13551</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-11.82674</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.12656</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>582338</t>
+          <t>145828</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LUISA ASTRAIN</t>
+          <t>ARTURO PADILLA ESPINOZA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.835376</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.174816</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>-11.86003</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.124549</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>722895</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>HARRY SULLIVAN</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-11.848</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.1401</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>-11.937548</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.1342</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>901712</t>
+          <t>145729</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>5156 ELIAS AGUIRRE ROMERO</t>
+          <t>CONSORCIO EDUCATIVO FK</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-11.839988</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-77.175173</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>-11.875674</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.123238</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>144758</t>
+          <t>145381</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>5118 COMANDANTE JUAN VALER SANDOVAL</t>
+          <t>FE Y ALEGRIA 29</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-11.876555</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.138679</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>-11.8748</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.1071</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>836750</t>
+          <t>145376</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA MERCED</t>
+          <t>AVHALDIM</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-11.82866</t>
+          <t>375</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.157281</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-11.869103</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.115948</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>594124</t>
+          <t>145220</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>5130-3 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>SAN JUDAS TADEO PATRON DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-11.938141</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.136459</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>-11.8777</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.135</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>319885</t>
+          <t>145178</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>SOPHIANO COLLEGE S.R.L.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-11.82674</t>
+          <t>428</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.12656</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>-11.8721</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.1281</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>593539</t>
+          <t>145164</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>5129 VENCEDORES DE PACHACUTEC</t>
+          <t>COLEGIO DE JESUS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.831957</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.147872</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>-11.887405</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.129215</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>144937</t>
+          <t>145140</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MARCELINO CHAMPAGNAT</t>
+          <t>FE Y ALEGRIA 43</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-11.887057</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.11967</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>-11.8223</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.1308</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>593983</t>
+          <t>144942</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>COPRODELI SAN FRANCISCO SOLANO</t>
+          <t>SAN PEDRO NOLASCO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-11.835969</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.160919</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>-11.878471</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.133828</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>594459</t>
+          <t>144937</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>5138 DEFENSORES DE LA PATRIA</t>
+          <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-11.8798</t>
+          <t>445</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.1378</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>-11.887057</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.11967</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>144517</t>
+          <t>144843</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4020 JOSE SANTOS CHOCANO</t>
+          <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-11.8709</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.1148</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>-11.882492</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.129906</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>594534</t>
+          <t>144824</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5124 LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-11.8776</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.1052</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>-11.833957</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.140243</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>611717</t>
+          <t>144819</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>COPRODELI SANTA MARIA ASUNTA AL CIELO</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-11.849816</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.145747</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>-11.831639</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.139366</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>144602</t>
+          <t>144800</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>5090 ANTONIA MORENO DE CACERES</t>
+          <t>5123 FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-11.89357</t>
+          <t>981</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.109993</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>-11.821738</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.138676</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>144800</t>
+          <t>144796</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>5123 FRANCISCO BOLOGNESI CERVANTES</t>
+          <t>5122 JOSE ANDRES RAZURI ESTEVEZ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.821738</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.138676</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>-11.84698</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.130321</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>625583</t>
+          <t>144782</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 76</t>
+          <t>5121 PEDRO PLANAS SILVA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.84773</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.145983</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>-11.825204</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.1362</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>144541</t>
+          <t>144777</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>5052 VIRGEN DE LA MERCED</t>
+          <t>5120 JOSE CARLOS MARIATEGUI LA CHIRA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.875876</t>
+          <t>458</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.124247</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>-11.83304</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.1254</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>145376</t>
+          <t>144758</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AVHALDIM</t>
+          <t>5118 COMANDANTE JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-11.869103</t>
+          <t>844</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.115948</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>-11.876555</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.138679</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>862664</t>
+          <t>144744</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON E.I.R.L.</t>
+          <t>5117 JORGE PORTOCARRERO REBAZA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-11.887075</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.120113</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>-11.844911</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.147329</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>509239</t>
+          <t>144701</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>5142 VIRGEN DE GUADALUPE</t>
+          <t>POLITECNICO VILLA LOS REYES</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.8425</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.1395</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>-11.8291</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.1267</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>320105</t>
+          <t>144697</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>3720 NUESTRA SEÑORA DE LA MISERICORDIA</t>
+          <t>NUESTRA SEÑORA DE BELEN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.825532</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.123596</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>-11.873055</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.119737</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>595171</t>
+          <t>144678</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>5141 DIVINO MAESTRO</t>
+          <t>LICEO NAVAL CAPITAN DE CORBETA MANUEL CLAVERO MUGA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.837874</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.124257</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>-11.888391</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-77.128991</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>144635</t>
+          <t>144664</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>5094 NACIONES UNIDAS</t>
+          <t>5116 DIVINO CREADOR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-11.827088</t>
+          <t>394</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.129217</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>-11.845586</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-77.125948</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6019,37 +6019,37 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>580283</t>
+          <t>144640</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ESCUELA HOGAR COMUNITARIA REGIONAL SAGRADA FAMILIA</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-11.827007</t>
+          <t>659</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.131846</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>-11.877161</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-77.116951</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6081,42 +6081,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>678883</t>
+          <t>144635</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>5094 NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-11.8464</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.1352</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>-11.827088</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-77.129217</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6143,37 +6143,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>144598</t>
+          <t>144621</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>5088 HEROES DEL PACIFICO</t>
+          <t>5093 ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.889443</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.130086</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>-11.885733</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-77.12378</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>144522</t>
+          <t>144616</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>5091 HIJOS DE GRAU</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-11.94362</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.114256</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>-11.886214</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-77.132396</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>144555</t>
+          <t>144602</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>5053 VICTOR ANDRES BELAUNDE</t>
+          <t>5090 ANTONIA MORENO DE CACERES</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-11.876105</t>
+          <t>787</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.125546</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>-11.89357</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.109993</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6329,37 +6329,37 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>144697</t>
+          <t>144598</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE BELEN</t>
+          <t>5088 HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-11.873055</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.119737</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>-11.889443</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.130086</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>144782</t>
+          <t>144584</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>5121 PEDRO PLANAS SILVA</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-11.825204</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.1362</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>-11.823805</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.127486</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>594435</t>
+          <t>144579</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 59</t>
+          <t>5086 POLITECNICO DE VENTANILLA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-11.84209</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.13436</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>-11.882365</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.130585</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>144796</t>
+          <t>144560</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>5122 JOSE ANDRES RAZURI ESTEVEZ</t>
+          <t>5077 JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-11.84698</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.130321</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>-11.8308</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-77.1225</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>145381</t>
+          <t>144555</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 29</t>
+          <t>5053 VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-11.8748</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.1071</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>-11.876105</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-77.125546</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>144560</t>
+          <t>144541</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>5077 JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>5052 VIRGEN DE LA MERCED</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-11.8308</t>
+          <t>931</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.1225</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>-11.875876</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-77.124247</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>144621</t>
+          <t>144536</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>5093 ANTONIO RAYMONDI</t>
+          <t>5051 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-11.885733</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.12378</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>-11.871104</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-77.114307</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>144824</t>
+          <t>144522</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>5124 LIBERTADOR SIMON BOLIVAR</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-11.833957</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-77.140243</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>-11.94362</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-77.114256</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>145140</t>
+          <t>144517</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 43</t>
+          <t>4020 JOSE SANTOS CHOCANO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-11.8223</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.1308</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>-11.8709</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-77.1148</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>144503</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>DIVINO NIÑO DE VILLA LOS REYES</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-11.831639</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-77.139366</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>-11.8282</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-77.122204</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>144701</t>
+          <t>144452</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>POLITECNICO VILLA LOS REYES</t>
+          <t>132 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-11.8291</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.1267</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>-11.898898</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-77.128252</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>144536</t>
+          <t>144447</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>5051 VIRGEN DE FATIMA</t>
+          <t>114 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-11.871104</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-77.114307</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>-11.824778</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-77.131233</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>593638</t>
+          <t>144409</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>5128 SAGRADO CORAZON DE MARIA</t>
+          <t>107 LOS PASTORCITOS DE FATIMA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-11.835</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-77.1597</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>-11.886057</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-77.132603</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7135,37 +7135,37 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>144744</t>
+          <t>144391</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>5117 JORGE PORTOCARRERO REBAZA</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-11.844911</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-77.147329</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>-11.87738</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>-77.11657</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>593940</t>
+          <t>144372</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>5130 PACHACUTEC</t>
+          <t>104 MI PEQUEÑO GRAN MUNDO</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-11.829203</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-77.155274</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>-11.890433</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-77.127141</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>144678</t>
+          <t>144367</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LICEO NAVAL CAPITAN DE CORBETA MANUEL CLAVERO MUGA</t>
+          <t>102 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-11.888391</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-77.128991</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>-11.943642</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-77.113999</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>506472</t>
+          <t>144348</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>5127 MARTIR JOSE OLAYA</t>
+          <t>93 VIRGEN MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-11.838755</t>
+          <t>339</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-77.123463</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>-11.875157</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-77.107255</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>144579</t>
+          <t>144334</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>5086 POLITECNICO DE VENTANILLA</t>
+          <t>83 AMIGOS DE JESUS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-11.882365</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-77.130585</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>-11.829997</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-77.120163</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>144305</t>
+          <t>144329</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>74 LOS PROCERES</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-11.872779</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-77.122767</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-11.866048</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.114449</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7507,37 +7507,37 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>144391</t>
+          <t>144305</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-11.87738</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-77.11657</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-11.872779</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.122767</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>623211</t>
+          <t>141868</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>123 VIRGEN DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-11.8546</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-77.140043</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-11.83615</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.158904</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">

--- a/ZonasEscolares/excels/CALLAO-CALLAO-VENTANILLA.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-VENTANILLA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
